--- a/template.xlsx
+++ b/template.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15660" windowHeight="10480" activeTab="1"/>
+    <workbookView windowWidth="20040" windowHeight="10200"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="othername" sheetId="3" r:id="rId2"/>
+    <sheet name="可识别的物品" sheetId="2" r:id="rId1"/>
+    <sheet name="别名" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$2:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">可识别的物品!$A$2:$D$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="26">
+  <si>
+    <t>要识别的物品增加在下方</t>
+  </si>
   <si>
     <t>商品名称</t>
   </si>
@@ -103,6 +106,9 @@
   </si>
   <si>
     <t>圆包,圆包菜</t>
+  </si>
+  <si>
+    <t>如果有别名，在B列用英文逗号隔开</t>
   </si>
 </sst>
 </file>
@@ -282,12 +288,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -623,7 +635,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -647,16 +659,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -665,96 +677,99 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1296,130 +1311,132 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="18.3365384615385" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.3365384615385" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.3365384615385" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.3365384615385" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.8942307692308" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:4">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
     </row>
     <row r="2" customHeight="1" spans="1:4">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" customHeight="1" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" customHeight="1" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="5" customHeight="1" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5</v>
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>5</v>
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5</v>
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5</v>
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
+      <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D11">
+  <autoFilter ref="A2:D14">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
@@ -1434,94 +1451,105 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.0961538461538" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6">
+      <c r="C18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C18:F18"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
